--- a/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos</t>
+          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 20,95</t>
+          <t>17,14; 21,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 19,87</t>
+          <t>13,74; 19,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 17,64</t>
+          <t>12,68; 17,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 23,66</t>
+          <t>12,35; 23,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 23,42</t>
+          <t>17,12; 23,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,51</t>
+          <t>17,22; 22,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 21,02</t>
+          <t>14,15; 21,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,71; 66,95</t>
+          <t>12,54; 57,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 21,52</t>
+          <t>17,61; 21,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 19,78</t>
+          <t>16,2; 20,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 18,54</t>
+          <t>14,18; 18,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 43,31</t>
+          <t>14,38; 36,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,58; 26,78</t>
+          <t>20,67; 26,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 22,95</t>
+          <t>16,95; 23,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 21,06</t>
+          <t>15,16; 20,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,48; 20,85</t>
+          <t>10,12; 20,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 25,3</t>
+          <t>19,65; 25,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 22,1</t>
+          <t>17,06; 22,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 21,1</t>
+          <t>13,63; 20,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 15,48</t>
+          <t>7,82; 15,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,79; 24,88</t>
+          <t>20,72; 24,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 21,5</t>
+          <t>17,57; 21,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 19,35</t>
+          <t>15,16; 19,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 15,99</t>
+          <t>9,75; 16,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 25,19</t>
+          <t>17,85; 25,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,19; 25,87</t>
+          <t>19,1; 25,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 24,41</t>
+          <t>15,37; 24,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 35,47</t>
+          <t>8,9; 38,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,94; 25,61</t>
+          <t>20,0; 26,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,11</t>
+          <t>17,04; 22,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,28; 19,13</t>
+          <t>14,12; 19,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 29,06</t>
+          <t>8,56; 27,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,67; 24,26</t>
+          <t>19,61; 24,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,53; 23,08</t>
+          <t>18,75; 22,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,19; 20,04</t>
+          <t>15,47; 20,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 26,7</t>
+          <t>9,5; 25,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 25,11</t>
+          <t>19,27; 24,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 24,3</t>
+          <t>19,68; 24,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,4; 20,23</t>
+          <t>15,29; 20,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 22,79</t>
+          <t>12,61; 23,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,33; 22,18</t>
+          <t>18,31; 22,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,32</t>
+          <t>18,85; 23,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,11; 22,72</t>
+          <t>16,06; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 28,83</t>
+          <t>13,57; 28,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 22,62</t>
+          <t>19,18; 22,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,89; 22,99</t>
+          <t>19,78; 22,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,27; 20,51</t>
+          <t>16,22; 20,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,55</t>
+          <t>14,26; 23,59</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,72; 29,02</t>
+          <t>20,94; 28,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,44</t>
+          <t>17,43; 22,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,74</t>
+          <t>15,69; 19,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,42; 47,51</t>
+          <t>13,28; 49,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,67; 25,48</t>
+          <t>19,61; 24,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 24,71</t>
+          <t>19,27; 24,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,03</t>
+          <t>15,57; 19,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 29,62</t>
+          <t>11,04; 27,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,64</t>
+          <t>20,84; 25,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,3</t>
+          <t>18,91; 22,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 19,2</t>
+          <t>16,11; 19,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 30,7</t>
+          <t>13,57; 30,6</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,32; 25,82</t>
+          <t>20,45; 25,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,41; 23,13</t>
+          <t>16,48; 23,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,62; 26,01</t>
+          <t>14,72; 25,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 12,68</t>
+          <t>4,31; 12,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 28,42</t>
+          <t>18,86; 28,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 24,58</t>
+          <t>16,66; 24,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,71</t>
+          <t>13,7; 18,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 15,79</t>
+          <t>6,29; 16,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,55; 25,69</t>
+          <t>20,44; 25,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 22,31</t>
+          <t>17,14; 22,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,78</t>
+          <t>14,94; 20,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,78</t>
+          <t>5,97; 12,5</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,62; 23,24</t>
+          <t>20,52; 23,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,89; 21,19</t>
+          <t>19,04; 21,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,54</t>
+          <t>16,09; 18,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 22,25</t>
+          <t>14,16; 22,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,13; 22,42</t>
+          <t>20,11; 22,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,25; 21,56</t>
+          <t>19,35; 21,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 18,63</t>
+          <t>16,14; 18,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 22,98</t>
+          <t>13,84; 23,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,61; 22,29</t>
+          <t>20,64; 22,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 21,07</t>
+          <t>19,4; 21,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,38; 18,14</t>
+          <t>16,41; 18,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 21,19</t>
+          <t>14,55; 20,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 21,16</t>
+          <t>17,03; 20,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,14</t>
+          <t>13,92; 19,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,74</t>
+          <t>12,85; 17,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 23,82</t>
+          <t>12,56; 24,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,12; 23,53</t>
+          <t>16,79; 22,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,65</t>
+          <t>17,16; 22,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 21,08</t>
+          <t>14,19; 21,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 57,85</t>
+          <t>12,96; 65,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 21,41</t>
+          <t>17,73; 21,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 20,01</t>
+          <t>16,16; 19,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 18,64</t>
+          <t>14,03; 18,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 36,04</t>
+          <t>14,26; 35,88</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 26,49</t>
+          <t>20,44; 26,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 23,15</t>
+          <t>17,2; 23,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 20,87</t>
+          <t>15,07; 20,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 20,36</t>
+          <t>10,19; 20,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 25,16</t>
+          <t>19,74; 24,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 22,18</t>
+          <t>16,86; 22,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 20,49</t>
+          <t>13,61; 20,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 15,22</t>
+          <t>7,91; 15,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 24,66</t>
+          <t>20,8; 24,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 21,54</t>
+          <t>17,56; 21,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 19,56</t>
+          <t>14,94; 19,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 16,43</t>
+          <t>9,77; 16,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,85; 25,89</t>
+          <t>17,72; 25,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 25,99</t>
+          <t>19,26; 26,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,37; 24,67</t>
+          <t>15,17; 24,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 38,38</t>
+          <t>9,39; 37,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 26,06</t>
+          <t>19,93; 25,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,22</t>
+          <t>16,76; 22,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 19,13</t>
+          <t>14,3; 19,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 27,66</t>
+          <t>9,0; 28,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,32</t>
+          <t>19,57; 24,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 22,89</t>
+          <t>18,59; 22,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,35</t>
+          <t>15,27; 20,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 25,02</t>
+          <t>9,98; 25,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 24,9</t>
+          <t>19,32; 24,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,68; 24,1</t>
+          <t>19,76; 23,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,47</t>
+          <t>15,28; 19,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 23,71</t>
+          <t>12,8; 23,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,5</t>
+          <t>18,31; 22,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 23,66</t>
+          <t>19,02; 23,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 22,93</t>
+          <t>16,08; 23,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 28,37</t>
+          <t>13,43; 27,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 22,46</t>
+          <t>19,3; 22,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,78; 22,9</t>
+          <t>19,85; 23,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,49</t>
+          <t>16,13; 20,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 23,59</t>
+          <t>14,31; 23,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 28,96</t>
+          <t>20,62; 29,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 22,33</t>
+          <t>17,31; 22,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 19,5</t>
+          <t>15,6; 19,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 49,63</t>
+          <t>13,16; 50,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,96</t>
+          <t>19,29; 24,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,27; 24,74</t>
+          <t>18,87; 24,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,57; 19,84</t>
+          <t>15,66; 19,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 27,73</t>
+          <t>11,31; 29,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,84; 25,62</t>
+          <t>20,77; 25,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,91; 22,52</t>
+          <t>18,64; 22,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 19,01</t>
+          <t>16,02; 18,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 30,6</t>
+          <t>13,56; 30,61</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,45; 25,71</t>
+          <t>20,3; 25,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,16</t>
+          <t>16,49; 23,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,72; 25,85</t>
+          <t>14,7; 26,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,34</t>
+          <t>4,2; 12,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,86; 28,97</t>
+          <t>19,36; 27,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,22</t>
+          <t>16,64; 24,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,7; 18,62</t>
+          <t>13,77; 18,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 16,55</t>
+          <t>6,41; 15,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,88</t>
+          <t>20,4; 25,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 22,22</t>
+          <t>17,48; 22,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,26</t>
+          <t>15,03; 20,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,5</t>
+          <t>6,05; 12,52</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 23,08</t>
+          <t>20,4; 22,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,04; 21,25</t>
+          <t>18,99; 21,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 18,43</t>
+          <t>16,1; 18,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 22,19</t>
+          <t>14,03; 23,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,11; 22,42</t>
+          <t>20,12; 22,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,35; 21,69</t>
+          <t>19,2; 21,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,8</t>
+          <t>15,96; 18,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,84; 23,2</t>
+          <t>13,51; 23,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,64; 22,35</t>
+          <t>20,69; 22,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 21,05</t>
+          <t>19,39; 20,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,41; 18,13</t>
+          <t>16,43; 18,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,7</t>
+          <t>14,55; 20,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Clase-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
+          <t>Tiempo medio en minutos que tuvieron que esperar desde que llegaron hasta ser atendidos/as en la última consulta médica (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24,24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,79</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,65</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,0</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,93</t>
+          <t>18,28</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,34</t>
+          <t>21,05</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 20,9</t>
+          <t>17,19; 23,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 19,3</t>
+          <t>17,23; 22,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,69</t>
+          <t>14,19; 21,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 24,06</t>
+          <t>12,04; 70,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 22,8</t>
+          <t>16,98; 20,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,52</t>
+          <t>13,92; 19,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 21,71</t>
+          <t>12,72; 17,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 65,94</t>
+          <t>13,82; 24,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,73; 21,21</t>
+          <t>17,71; 21,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 19,76</t>
+          <t>16,25; 19,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,46</t>
+          <t>14,04; 18,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 35,88</t>
+          <t>14,86; 46,16</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,05</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,91</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>23,22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,54</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,7</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,24</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,16</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,05</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>15,13</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,44; 26,33</t>
+          <t>19,8; 25,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 23,1</t>
+          <t>16,94; 22,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,91</t>
+          <t>13,68; 21,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,19; 20,2</t>
+          <t>7,85; 15,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 24,89</t>
+          <t>20,58; 26,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,86; 22,22</t>
+          <t>16,92; 22,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 20,55</t>
+          <t>15,08; 21,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 15,79</t>
+          <t>10,25; 20,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 24,9</t>
+          <t>20,79; 24,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 21,61</t>
+          <t>17,8; 21,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 19,36</t>
+          <t>15,11; 19,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,21</t>
+          <t>9,81; 16,02</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,54</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,21</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,36</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,46</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,35</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,88</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>14,27</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 25,23</t>
+          <t>19,94; 25,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 26,08</t>
+          <t>17,02; 22,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 24,39</t>
+          <t>14,28; 19,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 37,82</t>
+          <t>8,88; 28,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 25,8</t>
+          <t>17,67; 25,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,34</t>
+          <t>19,19; 25,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,07</t>
+          <t>15,2; 24,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 28,17</t>
+          <t>9,13; 35,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 24,22</t>
+          <t>19,67; 24,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 22,88</t>
+          <t>18,53; 23,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,38</t>
+          <t>15,19; 20,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 25,3</t>
+          <t>10,09; 24,81</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,03</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,97</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,59</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21,13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21,71</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,03</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,97</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,55</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,56</t>
+          <t>15,62</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,67</t>
+          <t>17,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,32; 24,99</t>
+          <t>18,33; 22,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 23,95</t>
+          <t>18,96; 23,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 19,92</t>
+          <t>16,11; 22,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,82</t>
+          <t>13,5; 28,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,63</t>
+          <t>19,29; 25,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 23,54</t>
+          <t>19,6; 24,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 23,16</t>
+          <t>15,4; 20,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 27,3</t>
+          <t>11,87; 21,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 22,79</t>
+          <t>19,25; 22,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 23,01</t>
+          <t>19,89; 22,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 20,15</t>
+          <t>16,27; 20,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,69</t>
+          <t>13,77; 22,81</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21,46</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,48</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,28</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>24,32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,44</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,44</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,84</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,46</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,48</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,91</t>
+          <t>21,93</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>19,27</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,62; 29,03</t>
+          <t>19,67; 25,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,31; 22,06</t>
+          <t>19,04; 24,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,6; 19,63</t>
+          <t>15,47; 20,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,16; 50,36</t>
+          <t>11,14; 31,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,89</t>
+          <t>20,72; 29,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 24,52</t>
+          <t>17,38; 22,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,66; 19,87</t>
+          <t>15,55; 19,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 29,41</t>
+          <t>13,31; 43,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,77; 25,28</t>
+          <t>20,8; 25,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,64; 22,36</t>
+          <t>18,82; 22,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,02; 18,83</t>
+          <t>16,11; 19,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 30,61</t>
+          <t>13,61; 30,28</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23,01</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19,66</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,97</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,69</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,75</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19,35</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17,59</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,4</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,01</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,97</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,5</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 25,75</t>
+          <t>19,14; 28,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,49; 23,01</t>
+          <t>16,76; 24,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,08</t>
+          <t>13,65; 18,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 12,85</t>
+          <t>5,93; 16,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,36; 27,91</t>
+          <t>20,32; 25,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,64; 24,19</t>
+          <t>16,41; 23,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,77; 18,6</t>
+          <t>14,62; 26,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 15,66</t>
+          <t>3,98; 12,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,4; 25,69</t>
+          <t>20,55; 25,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 22,33</t>
+          <t>17,32; 22,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,03; 20,4</t>
+          <t>14,8; 20,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,52</t>
+          <t>6,06; 12,92</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21,24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17,23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17,12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>21,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,05</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>17,16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,24</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,23</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,01</t>
+          <t>16,67</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,03</t>
+          <t>16,92</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,4; 22,99</t>
+          <t>20,13; 22,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,24</t>
+          <t>19,25; 21,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,45</t>
+          <t>16,11; 18,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,03; 23,2</t>
+          <t>13,52; 23,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,49</t>
+          <t>20,62; 23,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,2; 21,62</t>
+          <t>18,89; 21,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 18,64</t>
+          <t>16,13; 18,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,51; 23,8</t>
+          <t>13,9; 21,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,69; 22,51</t>
+          <t>20,61; 22,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 20,97</t>
+          <t>19,4; 21,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 18,17</t>
+          <t>16,38; 18,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,75</t>
+          <t>14,55; 20,81</t>
         </is>
       </c>
     </row>
